--- a/data_extactor/batch_10_fa/batch_0078_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0078_fa.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Apache HTTP Server | Autodesk AutoCAD | Facebook | نرم‌افزار گزارش‌دهی تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Minitab | نرم‌افزار SAP | نرم‌افزار گزارش‌دهی کارکرد زمانی</t>
+          <t>Apache HTTP Server | Autodesk AutoCAD | Facebook | نرم‌افزار گزارش‌دهی تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Minitab | نرم‌افزار SAP | نرم‌افزار گزارش‌دهی زمان</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,22 +513,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | امنیت و ایمنی عمومی | ریاضیات | تولید و فرآوری | زبان انگلیسی | مهندسی و فناوری</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | ریاضیات | تولید و فرآوری | زبان انگلیسی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | هماهنگی چند عضو | قدرت استاتیک | دقت کنترل | قدرت تنه | زبردستی دستی | بینایی نزدیک | انعطاف‌پذیری گسترده | استقامت | قدرت پویا | زبردستی انگشتان | تجسم فضایی | حساسیت به مشکلات | درک شفاهی</t>
+          <t>ثبات دست و بازو | هماهنگی چند عضو | قدرت ایستا | دقت کنترل | قدرت تنه | مهارت دستی | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت پویا | مهارت انگشتان | تجسم | حساسیت به مسئله | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | در معرض آلاینده‌ها | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض دمای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض تجهیزات خطرناک | اهمیت دقیق یا منظم بودن | در معرض ارتعاش کل بدن | در خودروی روباز یا تجهیزات در حال کار | صرف زمان برای خم کردن یا چرخاندن بدن | سلامت و ایمنی سایر کارگران</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض ارتعاش کل بدن | در یک وسیله نقلیه روباز یا کار با تجهیزات | صرف زمان برای خم کردن یا چرخاندن بدن | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>آجرچین‌ها و بلوک‌چین‌ها | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | برش‌دهندگان و هرس‌کنندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه برش و اسلایس | حفاران زمین، به جز نفت و گاز | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | کارگران سایش و پرداخت دستی | دستیاران--کارگران استخراج | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | لوله‌گذاران | اپراتورهای مته چرخشی، نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه اره‌کشی چوب | سنگ‌فرش‌کنندگان قطعه‌ای | سنگ‌تراشان و حکاکان سنگ، تولیدی | سنگ‌تراشان | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران | تیزکنندگان ابزار، سوهان‌کاران و تیزکنندگان | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>بنّایان آجرکار و بلوک‌کار | بنّایان سیمان‌کار و پرداخت‌کاران بتن | کارگران ساختمانی | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | حفاران زمین، به جز نفت و گاز | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | کارگران سنگ‌زنی و پرداخت دستی | دستیاران--کارگران استخراج | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | لوله‌گذاران | اپراتورهای مته چرخشی، نفت و گاز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | سنگ‌فرش‌کاران قطعه‌ای | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | بنّایان سنگ‌کار | کارگران و پرداخت‌کاران ترازو | کاشی‌کاران و سنگ‌کاران | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ</t>
+          <t>تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و پرسنلی</t>
+          <t>مکانیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>زبردستی دستی | هماهنگی چند عضو | بینایی نزدیک | حساسیت به مشکلات | بینایی دور | ثبات دست و بازو | دقت کنترل | قدرت استاتیک | قدرت تنه | انعطاف‌پذیری گسترده | ترتیب‌دهی اطلاعات | درک شفاهی | استقامت | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تعادل کلی بدن | زمان عکس‌العمل | کنترل نرخ سرعت | زبردستی انگشتان | توجه انتخابی | درک عمق | انعطاف‌پذیری بستار | استدلال قیاسی | بیان شفاهی | تجسم فضایی</t>
+          <t>مهارت دستی | هماهنگی چند عضو | بینایی نزدیک | حساسیت به مسئله | بینایی دور | ثبات دست و بازو | دقت کنترل | قدرت ایستا | قدرت تنه | انعطاف‌پذیری دامنه حرکت | ترتیب‌دهی اطلاعات | درک شفاهی | استقامت | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تعادل کلی بدن | زمان عکس‌العمل | کنترل نرخ | مهارت انگشتان | توجه انتخابی | درک عمق | انعطاف‌پذیری بستار | استدلال قیاسی | بیان شفاهی | تجسم</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض دمای بسیار گرم یا سرد | ارتباط با دیگران | فراوانی تصمیم‌گیری | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | فشار زمانی | فضای بسته، بدون کنترل دما | صرف زمان به صورت ایستاده | در معرض آلاینده‌ها | سلامت و ایمنی سایر کارگران | پیامدهای کاری و نتایج سایر کارگران | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم کردن یا چرخاندن بدن | اهمیت دقیق یا منظم بودن | در معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | پیامد خطا | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | ارتباط با دیگران | فراوانی تصمیم‌گیری | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فشار زمانی | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای خم کردن یا چرخاندن بدن | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | پیامد خطا | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورهای دکل، نفت و گاز | حفاران زمین، به جز نفت و گاز | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان موتور و سایر ماشین‌آلات | اپراتورهای ماشین‌های حفاری، بارگیری و دراگ‌لاین، معدن‌کاری سطحی | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--لوله‌کشان، لوله‌کشان صنعتی، نصابان لوله و لوله‌کشان بخار | اپراتورهای بالابر و وینچ | کارگران تعمیر و نگهداری ماشین‌آلات | سازندگان آسیاب صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای شمع‌کوب | لوله‌کشان، لوله‌کشان صنعتی و لوله‌کشان بخار | دکل‌بندها | اپراتورهای مته چرخشی، نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | پمپ‌کنندگان سر چاه</t>
+          <t>کارگران ساختمانی | اپراتورهای دکل، نفت و گاز | حفاران زمین، به جز نفت و گاز | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | دستیاران--برق‌کاران | دستیاران--کارگران استخراج | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | اپراتورهای بالابر و وینچ | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | ریگرها | اپراتورهای مته چرخشی، نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | پمپ‌کنندگان سرچاهی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>دستیار اپراتور ماشین استخراج مداوم | دستیار حفار | دستیار کمک‌حفار | دستیار اپراتور ماشین دیواره بلند | دستیار معدن‌کار | باروت‌کار | معدن‌کار نمک | دستیار حفاری</t>
+          <t>دستیار اپراتور ماشین استخراج مداوم | دستیار حفار | دستیار کمک‌حفار | دستیار اپراتور ماشین دیواره بلند | دستیار معدن‌کار | باروت‌کار | معدن‌کار نمک</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | گوش دادن فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | حمل‌ونقل | ریاضیات</t>
+          <t>مکانیک | زبان انگلیسی | حمل و نقل | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>زبردستی دستی | ثبات دست و بازو | هماهنگی چند عضو | زمان عکس‌العمل | دقت کنترل | قدرت استاتیک | حساسیت به مشکلات | بینایی نزدیک | بینایی دور | قدرت تنه | درک عمق | کنترل نرخ سرعت | زبردستی انگشتان | درک شفاهی | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری گسترده | استقامت | جهت‌گیری پاسخ | تجسم فضایی | سرعت ادراکی | استدلال قیاسی | توجه شنیداری | حساسیت شنوایی | تشخیص گفتار | تعادل کلی بدن | هماهنگی کلی بدن | قدرت پویا | جهت‌گیری فضایی | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی</t>
+          <t>مهارت دستی | ثبات دست و بازو | هماهنگی چند عضو | زمان عکس‌العمل | دقت کنترل | قدرت ایستا | حساسیت به مسئله | بینایی نزدیک | بینایی دور | قدرت تنه | درک عمق | کنترل نرخ | مهارت انگشتان | درک شفاهی | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دامنه حرکت | استقامت | جهت‌گیری پاسخ | تجسم | سرعت ادراکی | استدلال قیاسی | توجه شنیداری | حساسیت شنوایی | تشخیص گفتار | تعادل کلی بدن | هماهنگی کلی بدن | قدرت پویا | جهت‌گیری فضایی | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در معرض تجهیزات خطرناک | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در معرض آلاینده‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | فضای بسته، بدون کنترل دما | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض دمای بسیار گرم یا سرد | ارتباط با دیگران | در معرض شرایط خطرناک | در خودروی روباز یا تجهیزات در حال کار | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | اهمیت دقیق یا منظم بودن | سرعت تعیین‌شده توسط سرعت تجهیزات | مکالمات تلفنی | پیامد خطا | پیامدهای کاری و نتایج سایر کارگران | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان به صورت ایستاده | در معرض سوختگی‌های جزئی، بریدگی‌ها، گزیدگی‌ها یا نیش‌زدگی‌ها | در معرض شرایط نوری بسیار روشن یا ناکافی</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض تجهیزات خطرناک | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | محیط داخلی، بدون کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | ارتباط با دیگران | قرار گرفتن در معرض شرایط خطرناک | در یک وسیله نقلیه روباز یا کار با تجهیزات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | اهمیت دقیق یا درست بودن | سرعت تعیین‌شده توسط سرعت تجهیزات | مکالمات تلفنی | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای ایستادن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری، بارگیری و دراگ‌لاین، معدن‌کاری سطحی | دستیاران--آجرچین‌ها، بلوک‌چین‌ها، سنگ‌تراشان و کاشی‌کاران و مرمرکاران | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--کارگران نصب، تعمیر و نگهداری | دستیاران--نقاشان، کاغذدیواری‌کنان، گچ‌کاران و سیمان‌کاران | دستیاران--لوله‌کشان، لوله‌کشان صنعتی، نصابان لوله و لوله‌کشان بخار | دستیاران--کارگران تولید | اپراتورهای بالابر و وینچ | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | تیزکنندگان ابزار، سوهان‌کاران و تیزکنندگان | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | دستیاران--بناهای آجر، بلوک، سنگ و نصابان کاشی و مرمر | دستیاران--نجاران | دستیاران--برق‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--نقاشان، کاغذدیواری‌کن‌ها، گچ‌کاران و بناهای گچ‌بری | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | کمک‌کاران--کارگران تولید | اپراتورهای بالابر و وینچ | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت کامپیوتری تعمیر و نگهداری CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن‌گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیک | امنیت و ایمنی عمومی | زبان انگلیسی | مهندسی و فناوری | ریاضیات | تولید و فرآوری | شیمی</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | زبان انگلیسی | مهندسی و فناوری | ریاضیات | تولید و فرآوری | شیمی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت استاتیک | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری گسترده | زمان عکس‌العمل | حساسیت به مشکلات | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض دمای بسیار گرم یا سرد | در معرض آلاینده‌ها | در معرض تجهیزات خطرناک | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارگران | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا منظم بودن | پیامد خطا | صرف زمان برای راه رفتن یا دویدن | در معرض سوختگی‌های جزئی، بریدگی‌ها، گزیدگی‌ها یا نیش‌زدگی‌ها | در معرض ارتعاش کل بدن | در معرض شرایط خطرناک</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | پیامد خطا | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض ارتعاش کل بدن | قرار گرفتن در معرض شرایط خطرناک</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>دستیاران--کارگران استخراج | کارگران فنی همه‌کاره نفت و گاز | اپراتورهای دکل، نفت و گاز | اپراتورهای مته چرخشی، نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | حفاران زمین، به جز نفت و گاز | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتش‌بارها | سنگ‌شکنان معدن | اپراتورهای ماشین‌های حفاری، بارگیری و دراگ‌لاین، معدن‌کاری سطحی | اپراتورهای ماشین استخراج مداوم | پیچ‌کنندگان سقف، معدن‌کاری | اپراتورهای ماشین‌های معدن‌کاری زیرزمینی، سایر | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | کارگران ساختمانی | پمپ‌کنندگان سر چاه | اپراتورهای پمپ، به جز پمپ‌کنندگان سر چاه | مهندسان معدن و زمین‌شناسی، از جمله مهندسان ایمنی معدن | مهندسان نفت | تکنسین‌های زمین‌شناسی، به جز تکنسین‌های هیدرولوژی</t>
+          <t>دستیاران--کارگران استخراج | کارگران فنی همه‌کاره نفت و گاز | اپراتورهای دکل، نفت و گاز | اپراتورهای مته چرخشی، نفت و گاز | اپراتورهای واحد خدمات، نفت و گاز | حفاران زمین، به جز نفت و گاز | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | سنگ‌شکنان معدن | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | اپراتورهای ماشین استخراج مداوم | پیچ‌کنندگان سقف، معدن | اپراتورهای ماشین‌های معدن‌کاری زیرزمینی، سایر | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | کارگران ساختمانی | پمپ‌کنندگان سرچاهی | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | مهندسان نفت | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | نرم‌افزار خودکار موجودی | نرم‌افزار حسابداری ساخت‌وساز ComputerEase | سیستم مدیریت کامپیوتری تعمیر و نگهداری CMMS | نرم‌افزار حسابداری بهای تمام شده | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | HCSS HeavyBid | HCSS HeavyJob | IBM Domino | IBM Notes | Infor ERP SyteLine | نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | نرم‌افزار حقوق و دستمزد | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار ثبت سوابق | نرم‌افزار SAP | نرم‌افزار برنامه‌ریزی | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار مدیریت خودرو | WorkTech MAXIMO | نرم‌افزار Yardi</t>
+          <t>Autodesk AutoCAD | نرم‌افزار خودکار موجودی | نرم‌افزار حسابداری ساخت‌وساز ComputerEase | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار حسابداری هزینه | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | HCSS HeavyBid | HCSS HeavyJob | IBM Domino | IBM Notes | Infor ERP SyteLine | نرم‌افزار مدیریت تعمیر و نگهداری | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | نرم‌افزار حقوق و دستمزد | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار ثبت سوابق | نرم‌افزار SAP | نرم‌افزار زمان‌بندی | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار مدیریت وسیله نقلیه | WorkTech MAXIMO | نرم‌افزار Yardi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>مانیتورینگ | سخن‌گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | استراتژی‌های یادگیری | نگارش</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مدیریت و اداره | مکانیک | خدمات مشتریان و پرسنلی | اداری | پرسنل و منابع انسانی | زبان انگلیسی | ریاضیات</t>
+          <t>مدیریت و اداره | مکانیک | خدمات مشتری و شخصی | اداری | پرسنل و منابع انسانی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مشکلات | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | بینایی دور | انعطاف‌پذیری دسته‌بندی | بیان کتبی | تجسم فضایی | سرعت ادراکی | توجه شنیداری | حساسیت شنوایی | دقت کنترل | زبردستی انگشتان | زبردستی دستی | ثبات دست و بازو | سهولت در کار با اعداد | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | بینایی دور | انعطاف‌پذیری دسته‌بندی | بیان کتبی | تجسم | سرعت ادراکی | توجه شنیداری | حساسیت شنوایی | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توانایی عددی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا منظم بودن | پیامدهای کاری و نتایج سایر کارگران | ایمیل | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | اهمیت تکرار وظایف یکسان | در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض تجهیزات خطرناک</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | ایمیل | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران تاسیسات | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران تفریحی و سرگرمی، به جز خدمات قمار | سرپرستان خط اول کارگران کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارگران تهیه و سرو غذا | سرپرستان خط اول دستیاران، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران محوطه‌سازی، خدمات چمن و نگهداری فضای سبز | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول کارگران فروش غیرخرده‌فروشی | سرپرستان خط اول کارگران پشتیبانی دفتری و اداری | سرپرستان خط اول همراهان مسافران | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان خط اول کارگران تولید و عملیات | سرپرستان خط اول کارگران امنیتی | مدیران کل و عملیاتی | فناوران و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | هماهنگ‌کنندگان بازیافت</t>
+          <t>مدیران تسهیلات | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیات | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | هماهنگ‌کنندگان بازیافت</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار ردیابی تماس | Cisco Systems VPN Client | نرم‌افزار پایگاه داده | نرم‌افزار اشکال‌زدایی | نرم‌افزار ایمیل | Extensible markup language XML | Extensible stylesheet language XSL | Hypertext markup language HTML | IBM Notes | IBM WebSphere | نرم‌افزار سیستم کنترل موجودی | JavaScript | Linux | Macromedia Cold Fusion | McNeel Rhinoceros 3D | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Exchange | Microsoft Hyperterminal | Microsoft Internet Explorer | Microsoft Office Live Meeting | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic.NET | Microsoft Windows | Microsoft Word | Norton AntiVirus | نرم‌افزار عیب‌یابی کامپیوتر شخصی | نرم‌افزار برنامه‌ریزی | ServiceNow | Structured query language SQL | Symantec Altiris Deployment Solution | Symantec Norton Utilities | نرم‌افزار شبیه‌ساز ترمینال | UNIX | نرم‌افزار شناسایی ویروس | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Acrobat | نرم‌افزار ردیابی تماس | Cisco Systems VPN Client | نرم‌افزار پایگاه داده | نرم‌افزار عیب‌یابی | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | زبان شیوه نامه توسعه‌پذیر XSL | زبان نشانه‌گذاری ابرمتن HTML | IBM Notes | IBM WebSphere | نرم‌افزار سیستم کنترل موجودی | JavaScript | Linux | Macromedia Cold Fusion | McNeel Rhinoceros 3D | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Exchange | Microsoft Hyperterminal | Microsoft Internet Explorer | Microsoft Office Live Meeting | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic.NET | Microsoft Windows | Microsoft Word | Norton AntiVirus | نرم‌افزار عیب‌یابی کامپیوتر شخصی | نرم‌افزار زمان‌بندی | ServiceNow | زبان پرس‌وجوی ساختاریافته SQL | Symantec Altiris Deployment Solution | Symantec Norton Utilities | نرم‌افزار شبیه‌سازی ترمینال | UNIX | نرم‌افزار شناسایی ویروس | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | سخن‌گفتن | درک مطلب | مانیتورینگ | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | خدمات مشتریان و پرسنلی | مکانیک | مهندسی و فناوری | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مکانیک | مهندسی و فناوری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مشکلات | درک کتبی | وضوح گفتار | تشخیص گفتار | زبردستی انگشتان | تجسم فضایی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | دقت کنترل | زبردستی دستی | ثبات دست و بازو | تشخیص رنگ بصری | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بیان کتبی</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | تجسم | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | دقت کنترل | مهارت دستی | ثبات دست و بازو | تشخیص رنگ بصری | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بیان کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | آزادی در تصمیم‌گیری | ایمیل | فضای بسته، مجهز به سیستم تهویه مطبوع | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | ارتباط با دیگران | فراوانی تصمیم‌گیری | اهمیت دقیق یا منظم بودن | صرف زمان به صورت ایستاده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی</t>
+          <t>مکالمات تلفنی | آزادی در تصمیم‌گیری | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>فناوران و تکنسین‌های مهندسی هوافضا و عملیات | نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های هوانوردی | فناوران و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | اپراتورهای ابزار کنترل عددی کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | فناوران و تکنسین‌های مهندسی برق و الکترونیک | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | فناوران و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکنندگان تجهیزات الکترومکانیکی | نصابان و تعمیرکاران تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | مکانیک‌های ماشین‌آلات صنعتی | تعمیرکاران تجهیزات پزشکی | اپراتورهای ماشین‌های اداری، به جز کامپیوتر | تکنسین‌های رباتیک | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | اپراتورهای ابزار کنترل عددی کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | مکانیک‌های ماشین‌آلات صنعتی | تعمیرکاران تجهیزات پزشکی | اپراتورهای ماشین‌های اداری، به جز رایانه | تکنسین‌های رباتیک | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AERONET calculator | Backbone.js | Caliper Maptitude | سیستم مدیریت کامپیوتری تعمیر و نگهداری CMMS | نرم‌افزار نقشه‌برداری موقعیت مکانی | نرم‌افزار مستندسازی تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | نرم‌افزار تحلیل سوئیپ | Zoho WebNMS Cell Tower Manager</t>
+          <t>AERONET calculator | Backbone.js | Caliper Maptitude | سیستم مدیریت نگهداری کامپیوتری CMMS | نرم‌افزار نقشه‌برداری موقعیت مکانی | نرم‌افزار مستندسازی تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | نرم‌افزار تحلیل سوئیپ | Zoho WebNMS Cell Tower Manager</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش دادن فعال | درک مطلب | مانیتورینگ | یادگیری فعال | نگارش</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مخابرات | خدمات مشتریان و پرسنلی | مکانیک | مدیریت و اداره | مهندسی و فناوری | زبان انگلیسی | امنیت و ایمنی عمومی | ریاضیات | ارتباطات و رسانه</t>
+          <t>رایانه و الکترونیک | مخابرات | خدمات مشتری و شخصی | مکانیک | مدیریت و اداره | مهندسی و فناوری | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | بینایی نزدیک | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | زبردستی انگشتان | تشخیص گفتار | درک شفاهی | زبردستی دستی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | وضوح گفتار | انعطاف‌پذیری گسترده | دقت کنترل | بینایی دور | توجه انتخابی | تجسم فضایی | بیان کتبی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت انگشتان | تشخیص گفتار | درک شفاهی | مهارت دستی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | وضوح گفتار | انعطاف‌پذیری دامنه حرکت | دقت کنترل | بینایی دور | توجه انتخابی | تجسم | بیان کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا منظم بودن | مکالمات تلفنی | ایمیل | ارتباط با دیگران | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | پیامد خطا | فضای باز، در معرض تمام شرایط آب و هوایی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فضای بسته، مجهز به سیستم تهویه مطبوع</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | مکالمات تلفنی | ایمیل | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | فضای باز، در معرض تمام شرایط آب و هوایی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های هوانوردی | تکنسین‌های پخش برنامه | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط برق الکتریکی | فناوران و تکنسین‌های مهندسی برق و الکترونیک | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، نیروگاه، پست برق و رله | مونتاژکنندگان تجهیزات الکترومکانیکی | نصابان و تعمیرکاران تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌های نورپردازی | توزیع‌کنندگان و دیسپچرهای برق | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | نصابان سیستم‌های امنیتی و اعلام حریق | تعمیرکاران علائم و سوئیچ‌های ریل | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران خطوط مخابراتی</t>
+          <t>نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های هوانوردی | تکنسین‌های پخش | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصابان و تعمیرکاران خطوط انتقال نیروی برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | مونتاژکاران تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌های نورپردازی | توزیع‌کنندگان و دیسپچرهای برق | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | تعمیرکاران سیگنال و سوزن ریل | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | نصابان و تعمیرکاران خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apache Struts | Autodesk AutoCAD | Cisco IOS | نرم‌افزار فایروال | Fluke ClearSight Analyzer | Fluke Networks Fluke TechEXPERT | Fluke Networks TechAdvisor Field Access System | سیستم‌های سیستم اطلاعات جغرافیایی GIS | IBM Domino | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار سیستم پروتکل انتقال صدا از طریق اینترنت VoIP</t>
+          <t>Apache Struts | Autodesk AutoCAD | Cisco IOS | نرم‌افزار فایروال | Fluke ClearSight Analyzer | Fluke Networks Fluke TechEXPERT | Fluke Networks TechAdvisor Field Access System | سیستم‌های سیستم اطلاعات جغرافیایی GIS | IBM Domino | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | مانیتورینگ | سخن‌گفتن | یادگیری فعال | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نظارت | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | مخابرات | کامپیوتر و الکترونیک | زبان انگلیسی | ریاضیات | امنیت و ایمنی عمومی | مکانیک | مهندسی و فناوری | آموزش و تربیت</t>
+          <t>خدمات مشتری و شخصی | مخابرات | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | مکانیک | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | درک شفاهی | بینایی نزدیک | تشخیص رنگ بصری | ثبات دست و بازو | زبردستی دستی | زبردستی انگشتان | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | هماهنگی چند عضو | بیان شفاهی | انعطاف‌پذیری بستار | بینایی دور | سرعت ادراکی | تجسم فضایی | دقت کنترل | انعطاف‌پذیری دسته‌بندی | درک کتبی | انعطاف‌پذیری گسترده | توجه انتخابی | توجه شنیداری | درک عمق | تعادل کلی بدن | هماهنگی کلی بدن | قدرت تنه | قدرت استاتیک | سرعت بستار | روان بودن ایده‌ها | حفظ کردن</t>
+          <t>حساسیت به مسئله | درک شفاهی | بینایی نزدیک | تشخیص رنگ بصری | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | هماهنگی چند عضو | بیان شفاهی | انعطاف‌پذیری بستار | بینایی دور | سرعت ادراکی | تجسم | دقت کنترل | انعطاف‌پذیری دسته‌بندی | درک کتبی | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | توجه شنیداری | درک عمق | تعادل کلی بدن | هماهنگی کلی بدن | قدرت تنه | قدرت ایستا | سرعت بستار | روانی ایده‌ها | حفظ کردن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | مکالمات تلفنی | فراوانی تصمیم‌گیری | ارتباط با دیگران | آزادی در تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت دقیق یا منظم بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت تکرار وظایف یکسان | در معرض تجهیزات خطرناک | در معرض دمای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض شرایط نوری بسیار روشن یا ناکافی | تعیین وظایف، اولویت‌ها و اهداف | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در معرض فضای کاری تنگ، موقعیت‌های نامناسب | صرف زمان به صورت ایستاده</t>
+          <t>ایمیل | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | مکالمات تلفنی | فراوانی تصمیم‌گیری | ارتباط با دیگران | آزادی در تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های هوانوردی | تکنسین‌های پخش برنامه | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | نصابان و تعمیرکاران خطوط برق الکتریکی | فناوران و تکنسین‌های مهندسی برق و الکترونیک | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، نیروگاه، پست برق و رله | نصابان و تعمیرکاران تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | مدیران سیستم‌های کامپیوتری و شبکه | توزیع‌کنندگان و دیسپچرهای برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | نصابان سیستم‌های امنیتی و اعلام حریق | تعمیرکاران علائم و سوئیچ‌های ریل | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران خطوط مخابراتی</t>
+          <t>نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های هوانوردی | تکنسین‌های پخش | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | نصابان و تعمیرکاران خطوط انتقال نیروی برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | مدیران شبکه و سیستم‌های کامپیوتری | توزیع‌کنندگان و دیسپچرهای برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | تعمیرکاران سیگنال و سوزن ریل | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Apache HTTP Server | Autodesk AutoCAD | نرم‌افزار تست سیستم اویونیک | C++ | نرم‌افزار عیب‌یابی کامپیوتر | Dassault Systemes CATIA | Linux | نرم‌افزار ثبت سوابق تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Oracle Java | نرم‌افزار SAP | ابزارهای توسعه نرم‌افزار | سیستم مدیریت داده‌های فنی TDMS | UNIX | نرم‌افزار Workday</t>
+          <t>Apache HTTP Server | Autodesk AutoCAD | نرم‌افزار تست سیستم اویونیک | C++ | نرم‌افزار تشخیص کامپیوتر | Dassault Systemes CATIA | Linux | نرم‌افزار ثبت تعمیر و نگهداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Oracle Java | نرم‌افزار SAP | ابزارهای توسعه نرم‌افزار | سیستم مدیریت داده‌های فنی TDMS | UNIX | نرم‌افزار Workday</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن‌گفتن | گوش دادن فعال | درک مطلب | نگارش | مانیتورینگ | یادگیری فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مکانیک | زبان انگلیسی | مهندسی و فناوری | خدمات مشتریان و پرسنلی | مخابرات | طراحی | ریاضیات | آموزش و تربیت | امنیت و ایمنی عمومی</t>
+          <t>رایانه و الکترونیک | مکانیک | زبان انگلیسی | مهندسی و فناوری | خدمات مشتری و شخصی | مخابرات | طراحی | ریاضیات | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | حساسیت به مشکلات | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | زبردستی انگشتان | بیان شفاهی | دقت کنترل | ثبات دست و بازو | تجسم فضایی | زبردستی دستی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک کتبی | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مهارت انگشتان | بیان شفاهی | دقت کنترل | ثبات دست و بازو | تجسم | مهارت دستی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | اهمیت دقیق یا منظم بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فضای بسته، مجهز به سیستم تهویه مطبوع | ارتباط با دیگران | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش, محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | فراوانی تصمیم‌گیری | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | پیامد خطا | در معرض آلاینده‌ها | در معرض شرایط خطرناک</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | فراوانی تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | پیامد خطا | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض شرایط خطرناک</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>فناوران و تکنسین‌های مهندسی هوافضا و عملیات | مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | متصدیان خدمات هواپیما | مونتاژکنندگان سازه، سطوح، دکل‌بندی و سیستم‌های هواپیما | تکنسین‌های مهندسی خودرو | فناوران و تکنسین‌های کالیبراسیون | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | فناوران و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | فناوران و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکنندگان تجهیزات الکترومکانیکی | نصابان و تعمیرکاران تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | مونتاژکنندگان موتور و سایر ماشین‌آلات | تکنسین‌های نورپردازی | مهندسان مکانیک | تکنسین‌های رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | متصدیان خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌های مهندسی خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | مهندسان الکترونیک، به جز کامپیوتر | مونتاژکاران موتور و سایر ماشین‌آلات | تکنسین‌های نورپردازی | مهندسان مکانیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | نرم‌افزار پروفایل‌سازی کموتاتور | سیستم مدیریت کامپیوتری تعمیر و نگهداری CMMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار تست موتور | Python | نرم‌افزار SAP</t>
+          <t>Autodesk AutoCAD | نرم‌افزار پروفایل‌سازی کموتاتور | سیستم مدیریت نگهداری کامپیوتری CMMS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار تست موتور | Python | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | سخن‌گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | زبان انگلیسی | مدیریت و اداره | خدمات مشتریان و پرسنلی</t>
+          <t>مکانیک | تولید و فرآوری | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>زبردستی انگشتان | حساسیت به مشکلات | بینایی نزدیک | زبردستی دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | تجسم فضایی | تشخیص رنگ بصری | استدلال قیاسی | حساسیت شنوایی | استدلال استقرایی | درک کتبی | درک شفاهی | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار | انعطاف‌پذیری گسترده | کنترل نرخ سرعت | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | درک عمق | بیان شفاهی</t>
+          <t>مهارت انگشتان | حساسیت به مسئله | بینایی نزدیک | مهارت دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | تجسم | تشخیص رنگ بصری | استدلال قیاسی | حساسیت شنوایی | استدلال استقرایی | درک کتبی | درک شفاهی | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار | انعطاف‌پذیری دامنه حرکت | کنترل نرخ | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | درک عمق | بیان شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در معرض آلاینده‌ها | اهمیت دقیق یا منظم بودن | صرف زمان به صورت ایستاده | فراوانی تصمیم‌گیری | فضای بسته، بدون کنترل دما | آزادی در تصمیم‌گیری | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در معرض تجهیزات خطرناک | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در معرض شرایط خطرناک | در معرض سوختگی‌های جزئی، بریدگی‌ها، گزیدگی‌ها یا نیش‌زدگی‌ها | مکالمات تلفنی | صرف زمان برای انجام حرکات تکراری | پیامد خطا</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | آزادی در تصمیم‌گیری | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض تجهیزات خطرناک | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | مکالمات تلفنی | صرف زمان برای انجام حرکات تکراری | پیامد خطا</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، دکل‌بندی و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی، نیروگاه، پست برق و رله | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | دستیاران--کارگران نصب، تعمیر و نگهداری | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | سازندگان آسیاب صنعتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های تجهیزات برقی فضای باز و سایر موتورهای کوچک | تعمیرکاران واگن ریل | مونتاژکنندگان و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری سخت و لحیم‌کاری نرم</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | دستیاران--کارگران نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | تعمیرکنندگان واگن‌های ریلی | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0078_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0078_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | هماهنگی اندام‌ها | قدرت ایستا | دقت کنترل | قدرت تنه | چابکی دستی | دید نزدیک | انعطاف‌پذیری دامنه‌ای | استقامت بدنی | قدرت پویا | چابکی انگشتان | تجسم فضایی | حساسیت به مسئله | درک شفاهی</t>
+          <t>ثبات دست و بازو | هماهنگی چند عضو | قدرت ایستا | دقت کنترل | قدرت تنه | مهارت دستی | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | استقامت | قدرت پویا | مهارت انگشتان | تجسم | حساسیت به مسئله | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بنایان آجرچین و بلوک‌چین | سیمان‌کاران و پرداخت‌کاران بتن | کارگران ساختمانی | برش‌کاران دستی قطعات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش و ورقه‌کنی | حفاران زمین، به جز نفت و گاز | قالب‌ریزان و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران و سنگ‌زن‌های دستی | کارگران کمکی استخراج معدن | قالب‌ریزان و شکل‌دهندگان مواد، به جز فلز و پلاستیک | لوله‌گذاران | اپراتورهای دکل حفاری چرخشی نفت و گاز | تنظیم‌کنندگان، اپراتورها و مراقبان اره‌های چوب‌بری | سنگ‌فرش‌کاران قطعه‌ای | برش‌کاران و حکاکان سنگ در کارخانه‌ها | سنگ‌تراشان سنتی | موزاییک‌سازان و پرداخت‌کاران موزاییک درجا | کاشی‌کاران و سنگ‌کاران ساختمانی | ابزارتیزکن‌ها و سنباده‌کاران | تنظیم‌کنندگان و اپراتورهای ماشین‌های نجاری، به جز اره‌کشی</t>
+          <t>بنایان و سفت‌کاران ساختمان | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | حفاران زمین، به‌جز نفت و گاز | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | کارگران کمکی استخراج معدن | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | لوله‌گذاران خطوط انتقال | حفاران دورانی نفت و گاز | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | سنگ‌تراشان و حکاکان صنعتی سنگ | سنگ‌کاران ساختمانی | موزاییک‌کاران و پرداخت‌کاران terrazzo | کاشی‌کاران و سنگ‌کاران ظریف | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -570,12 +570,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی</t>
+          <t>مکانیک | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>چابکی دستی | هماهنگی اندام‌ها | دید نزدیک | حساسیت به مسئله | دید دور | ثبات دست و بازو | دقت کنترل | قدرت ایستا | قدرت تنه | انعطاف‌پذیری دامنه‌ای | مرتب‌سازی اطلاعات | درک شفاهی | استقامت بدنی | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تعادل عمومی بدن | زمان واکنش | کنترل نرخ سرعت | چابکی انگشتان | توجه انتخابی | درک عمق | انعطاف‌پذیری در بستن الگوها | استدلال قیاسی | بیان شفاهی | تجسم فضایی</t>
+          <t>مهارت دستی | هماهنگی چند عضو | بینایی نزدیک | حساسیت به مسئله | بینایی دور | ثبات دست و بازو | دقت کنترل | قدرت ایستا | قدرت تنه | انعطاف‌پذیری دامنه حرکت | ترتیب‌دهی اطلاعات | درک شفاهی | استقامت | تشخیص گفتار | توجه شنیداری | حساسیت شنوایی | تعادل کلی بدن | زمان عکس‌العمل | کنترل نرخ | مهارت انگشتان | توجه انتخابی | درک عمق | انعطاف‌پذیری بستار | استدلال قیاسی | بیان شفاهی | تجسم</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورهای دکل حفاری نفت و گاز | حفاران زمین، به جز نفت و گاز | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و ماشین‌آلات | اپراتورهای ماشین‌های حفاری، بارگیری و درگ‌لاین در معادن روباز | کارگران کمکی برق‌کار | کارگران کمکی استخراج معدن | کارگران کمکی لوله‌کشان صنعتی و تأسیساتی | اپراتورهای بالابر و وینچ | کارگران تعمیرات و نگهداری ماشین‌آلات | نصابان و تعمیرکاران ماشین‌آلات صنعتی (میلرایت) | مکانیک‌های ماشین‌آلات سنگین متحرک، به جز موتور | مهندسان اپراتور و رانندگان ماشین‌آلات سنگین عمرانی | اپراتورهای دستگاه شمع‌کوب | لوله‌کشان صنعتی، لوله‌کشان تأسیساتی و بخارکاران | باربندها و ریگرها | اپراتورهای دکل حفاری چرخشی نفت و گاز | اپراتورهای دستگاه‌های خدمات سرچاهی نفت و گاز | اپراتورهای پمپ‌های سرچاهی</t>
+          <t>کارگران ساختمانی | دکل‌بانان نفت و گاز | حفاران زمین، به‌جز نفت و گاز | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کمک‌برق‌کاران | کارگران کمکی استخراج معدن | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | اپراتورهای بالابر و وینچ | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای دستگاه شمع‌کوب | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | حفاران دورانی نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | اپراتورهای پمپ سرچاهی نفت و گاز</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,27 +612,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>کمک‌اپراتور دستگاه استخراج مداوم | کمک‌حفار معدن | دستیار حفار | کمک‌اپراتور دستگاه استخراج جبهه‌کار طولانی | کارگر کمکی معدن | کمک‌آتشبار معدن | کارگر معدن نمک</t>
+          <t>دستیار اپراتور ماشین استخراج مداوم | دستیار حفار | دستیار کمک‌حفار | دستیار اپراتور ماشین دیواره بلند | دستیار معدن‌کار | باروت‌کار | معدن‌کار نمک</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | Google Docs | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Outlook</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Outlook</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | ترابری و حمل‌ونقل | ریاضیات</t>
+          <t>مکانیک | زبان انگلیسی | حمل و نقل | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | هماهنگی اندام‌ها | زمان واکنش | دقت کنترل | قدرت ایستا | حساسیت به مسئله | دید نزدیک | دید دور | قدرت تنه | درک عمق | کنترل نرخ سرعت | چابکی انگشتان | درک شفاهی | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری دامنه‌ای | استقامت بدنی | جهت‌یابی پاسخ | تجسم فضایی | سرعت ادراک | استدلال قیاسی | توجه شنیداری | حساسیت شنوایی | تشخیص گفتار | تعادل عمومی بدن | هماهنگی کل بدن | قدرت پویا | جهت‌یابی فضایی | انعطاف‌پذیری در بستن الگوها | استدلال استقرایی | بیان شفاهی</t>
+          <t>مهارت دستی | ثبات دست و بازو | هماهنگی چند عضو | زمان عکس‌العمل | دقت کنترل | قدرت ایستا | حساسیت به مسئله | بینایی نزدیک | بینایی دور | قدرت تنه | درک عمق | کنترل نرخ | مهارت انگشتان | درک شفاهی | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دامنه حرکت | استقامت | جهت‌گیری پاسخ | تجسم | سرعت ادراکی | استدلال قیاسی | توجه شنیداری | حساسیت شنوایی | تشخیص گفتار | تعادل کلی بدن | هماهنگی کلی بدن | قدرت پویا | جهت‌گیری فضایی | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورهای ماشین‌های استخراج مداوم معدن | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری، بارگیری و درگ‌لاین در معادن روباز | کارگران کمکی بنایی، بلوک‌چینی، سنگ‌کاری و کاشی‌کاری | کارگران کمکی نجار | کارگران کمکی برق‌کار | کارگران کمکی نصب، تعمیرات و نگهداری | کارگران کمکی نقاش، کاغذدیواری‌کار و گچ‌کار | کارگران کمکی لوله‌کشان صنعتی و تأسیساتی | کارگران کمکی خطوط تولید | اپراتورهای بالابر و وینچ | باردهندگان و جابه‌جاگران مواد در ماشین‌آلات صنعتی | کارگران تعمیرات و نگهداری ماشین‌آلات | مهندسان اپراتور و رانندگان ماشین‌آلات سنگین عمرانی | اپراتورهای دکل حفاری چرخشی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | اپراتورهای دستگاه‌های خدمات سرچاهی نفت و گاز | ابزارتیزکن‌ها و سنباده‌کاران | تنظیم‌کنندگان و اپراتورهای ماشین‌های نجاری، به جز اره‌کشی</t>
+          <t>کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | کمک‌نجاران | کمک‌برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌نقاشان، کمک‌کاغذدیواری‌کاران، کمک‌گچ‌کاران و کمک‌سیمان‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | کمک‌کارگران خطوط تولید | اپراتورهای بالابر و وینچ | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | حفاران دورانی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی اندام‌ها | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت بدنی | دید نزدیک | دید دور | درک عمق | هماهنگی کل بدن | تعادل عمومی بدن | انعطاف‌پذیری دامنه‌ای | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارگران کمکی استخراج معدن | کارگران عمومی سکو و میادین نفت و گاز | اپراتورهای دکل حفاری نفت و گاز | اپراتورهای دکل حفاری چرخشی نفت و گاز | اپراتورهای دستگاه‌های خدمات سرچاهی نفت و گاز | حفاران زمین، به جز نفت و گاز | آتشباران، کارشناسان جابه‌جایی مهمات و مواد منفجره | سنگ‌شکنان و برش‌کاران سنگ معدن | اپراتورهای ماشین‌های حفاری، بارگیری و درگ‌لاین در معادن روباز | اپراتورهای ماشین‌های استخراج مداوم معدن | نصابان انکر و بولت سقف در معدن | سایر اپراتورهای ماشین‌های استخراج زیرزمینی | سرپرستان رده‌اول مشاغل ساختمانی و کارگران استخراج | مهندسان اپراتور و رانندگان ماشین‌آلات سنگین عمرانی | کارگران ساختمانی | اپراتورهای پمپ‌های سرچاهی | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | مهندسان نفت | تکنسین‌های زمین‌شناسی، به جز آب‌شناسی</t>
+          <t>کارگران کمکی استخراج معدن | کارگران عمومی سکو و میادین نفت و گاز | دکل‌بانان نفت و گاز | حفاران دورانی نفت و گاز | اپراتورهای واحدهای خدمات چاه نفت و گاز | حفاران زمین، به‌جز نفت و گاز | کارشناسان مواد منفجره و آتش‌باری | سنگ‌شکنان و برش‌کاران سنگ معدن | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | اپراتورهای ماشین‌های استخراج پیوسته | راک‌بولت‌کاران معدن | سایر اپراتورهای ماشین‌آلات استخراج در معادن زیرزمینی | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | کارگران ساختمانی | اپراتورهای پمپ سرچاهی نفت و گاز | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | مهندسان نفت | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | یادگیری فعال | استراتژی‌های یادگیری | نگارش</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | مکانیک | خدمات مشتریان و خدمات فردی | امور دفتری | منابع انسانی و امور پرسنلی | زبان انگلیسی | ریاضیات</t>
+          <t>مدیریت و اداره | مکانیک | خدمات مشتری و شخصی | اداری | پرسنل و منابع انسانی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | انعطاف‌پذیری در بستن الگوها | توجه انتخابی | دید دور | انعطاف‌پذیری طبقه‌بندی | بیان کتبی | تجسم فضایی | سرعت ادراک | توجه شنیداری | حساسیت شنوایی | دقت کنترل | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | تسهیلات محاسباتی | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | بینایی دور | انعطاف‌پذیری دسته‌بندی | بیان کتبی | تجسم | سرعت ادراکی | توجه شنیداری | حساسیت شنوایی | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توانایی عددی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران تأسیسات | سرپرستان رده‌اول مشاغل ساختمانی و کارگران استخراج | سرپرستان رده‌اول کارکنان خدمات سرگرمی و تفریحی، به جز مراکز بازی | سرپرستان رده‌اول کارکنان کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران کمکی، باربران و جابه‌جاگران دستی کالا | سرپرستان رده‌اول کارکنان خدمات نظافتی و خدماتی | سرپرستان رده‌اول کارگران محوطه‌سازی، فضای سبز و باغبانی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی کالا | سرپرستان رده‌اول فروشندگان بخش غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان امور دفتری و پشتیبانی اداری | سرپرستان رده‌اول مهمانداران و مهمان‌پذیران مسافرتی | سرپرستان رده‌اول کارکنان خدمات شخصی | سرپرستان رده‌اول کارکنان تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و نگهبانی | مدیران اجرایی و عملیاتی | مهندسان و تکنسین‌های فناوری مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | هماهنگ‌کنندگان بازیافت</t>
+          <t>مدیران امور ساختمان و تأسیسات | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیات | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | هماهنگ‌کنندگان امور بازیافت</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مکانیک | مهندسی و فناوری | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مکانیک | مهندسی و فناوری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | تجسم فضایی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | دقت کنترل | چابکی دستی | ثبات دست و بازو | تشخیص رنگ‌ها | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | بیان کتبی</t>
+          <t>بینایی نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | تجسم | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | دقت کنترل | مهارت دستی | ثبات دست و بازو | تشخیص رنگ بصری | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بیان کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری مهندسی هوافضا و عملیات پرواز | نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های اویونیک (الکترونیک پرواز) | کارشناسان و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، خودکار فروش و تفریحی | اپراتورهای ماشین‌های ابزار CNC | متخصصان پشتیبانی کاربران رایانه (Help Desk) | تکنسین‌های مهندسی برق و الکترونیک | نصابان و تعمیرکاران سیستم‌های برقی و الکترونیکی تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | مهندسان الکترونیک، به جز رایانه | مکانیک‌های ماشین‌آلات صنعتی | تعمیرکاران تجهیزات پزشکی | اپراتورهای ماشین‌های اداری، به جز رایانه | تکنسین‌های رباتیک | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | متخصصان پشتیبانی کاربران رایانه | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مهندسان الکترونیک، به‌جز کامپیوتر | مکانیک‌های ماشین‌آلات صنعتی | تعمیرکاران تجهیزات پزشکی | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | تکنسین‌های رباتیک | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت | یادگیری فعال | نگارش</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مخابرات | خدمات مشتریان و خدمات فردی | مکانیک | مدیریت و امور اداری | مهندسی و فناوری | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | ارتباطات و رسانه</t>
+          <t>رایانه و الکترونیک | مخابرات | خدمات مشتری و شخصی | مکانیک | مدیریت و اداره | مهندسی و فناوری | زبان انگلیسی | ایمنی و امنیت عمومی | ریاضیات | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | ثبات دست و بازو | مرتب‌سازی اطلاعات | استدلال قیاسی | چابکی انگشتان | تشخیص گفتار | درک شفاهی | چابکی دستی | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | وضوح گفتار | انعطاف‌پذیری دامنه‌ای | دقت کنترل | دید دور | توجه انتخابی | تجسم فضایی | بیان کتبی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت انگشتان | تشخیص گفتار | درک شفاهی | مهارت دستی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | وضوح گفتار | انعطاف‌پذیری دامنه حرکت | دقت کنترل | بینایی دور | توجه انتخابی | تجسم | بیان کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های اویونیک (الکترونیک پرواز) | تکنسین‌های پخش صدا و تصویر | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | سیم‌بانان و تعمیرکاران خطوط انتقال نیرو | تکنسین‌های مهندسی برق و الکترونیک | نصابان و تعمیرکاران سیستم‌های برقی و الکترونیکی تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی نیروگاه‌ها، پست‌ها و رله‌ها | مونتاژکاران تجهیزات الکترومکانیکی | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | مهندسان الکترونیک، به جز رایانه | تکنسین‌های نور و روشنایی | توزیع‌کنندگان و دیسپچرهای شبکه برق | متخصصان سیستم‌های شناسایی با امواج رادیویی (RFID) | نصابان سیستم‌های دزدگیر و اعلام حریق | تعمیرکاران سیستم‌های سیگنالینگ و سوزن‌بانی راه‌آهن | مهندسان و متخصصان شبکه و تجهیزات مخابراتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | سیم‌بانان و نصابان خطوط کابل مخابراتی</t>
+          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌های پخش و اتاق فرمان | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | مونتاژکاران تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مهندسان الکترونیک، به‌جز کامپیوتر | تکنسین‌های نورپردازی | دیسپچرها و توزیع‌کنندگان شبکه برق | متخصصان سامانه‌های شناسایی با امواج رادیویی | نصاب سیستم‌های اعلام سرقت و حریق | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | نصابان و کابل‌کشان خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | نظارت | سخن گفتن | یادگیری فعال | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نظارت | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مخابرات | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | مکانیک | مهندسی و فناوری | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | مخابرات | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | مکانیک | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | دید نزدیک | تشخیص رنگ‌ها | ثبات دست و بازو | چابکی دستی | چابکی انگشتان | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | هماهنگی اندام‌ها | بیان شفاهی | انعطاف‌پذیری در بستن الگوها | دید دور | سرعت ادراک | تجسم فضایی | دقت کنترل | انعطاف‌پذیری طبقه‌بندی | درک کتبی | انعطاف‌پذیری دامنه‌ای | توجه انتخابی | توجه شنیداری | درک عمق | تعادل عمومی بدن | هماهنگی کل بدن | قدرت تنه | قدرت ایستا | سرعت در بستن الگوها | روانی ایده‌ها | حافظه و یادآوری</t>
+          <t>حساسیت به مسئله | درک شفاهی | بینایی نزدیک | تشخیص رنگ بصری | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | هماهنگی چند عضو | بیان شفاهی | انعطاف‌پذیری بستار | بینایی دور | سرعت ادراکی | تجسم | دقت کنترل | انعطاف‌پذیری دسته‌بندی | درک کتبی | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | توجه شنیداری | درک عمق | تعادل کلی بدن | هماهنگی کلی بدن | قدرت تنه | قدرت ایستا | سرعت بستار | روانی ایده‌ها | حفظ کردن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های اویونیک (الکترونیک پرواز) | تکنسین‌های پخش صدا و تصویر | معماران شبکه‌های کامپیوتری | کارشناسان پشتیبانی شبکه | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | سیم‌بانان و تعمیرکاران خطوط انتقال نیرو | تکنسین‌های مهندسی برق و الکترونیک | نصابان و تعمیرکاران سیستم‌های برقی و الکترونیکی تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی نیروگاه‌ها، پست‌ها و رله‌ها | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | مهندسان الکترونیک، به جز رایانه | مدیران شبکه و سیستم‌های کامپیوتری | توزیع‌کنندگان و دیسپچرهای شبکه برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | نصابان سیستم‌های دزدگیر و اعلام حریق | تعمیرکاران سیستم‌های سیگنالینگ و سوزن‌بانی راه‌آهن | مهندسان و متخصصان شبکه و تجهیزات مخابراتی | سیم‌بانان و نصابان خطوط کابل مخابراتی</t>
+          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌های پخش و اتاق فرمان | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مهندسان الکترونیک، به‌جز کامپیوتر | مدیران شبکه و سیستم‌های کامپیوتری | دیسپچرها و توزیع‌کنندگان شبکه برق | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | نصاب سیستم‌های اعلام سرقت و حریق | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | متخصصان مهندسی مخابرات | نصابان و کابل‌کشان خطوط مخابراتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مکانیک | زبان انگلیسی | مهندسی و فناوری | خدمات مشتریان و خدمات فردی | مخابرات | طراحی | ریاضیات | آموزش و تدریس | ایمنی و امنیت عمومی</t>
+          <t>رایانه و الکترونیک | مکانیک | زبان انگلیسی | مهندسی و فناوری | خدمات مشتری و شخصی | مخابرات | طراحی | ریاضیات | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | چابکی انگشتان | بیان شفاهی | دقت کنترل | ثبات دست و بازو | تجسم فضایی | چابکی دستی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ‌ها | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>درک کتبی | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مهارت انگشتان | بیان شفاهی | دقت کنترل | ثبات دست و بازو | تجسم | مهارت دستی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری مهندسی هوافضا و عملیات پرواز | مهندسان هوافضا | مکانیک‌ها و تکنسین‌های فنی هواپیما | مهمانداران و پرسنل خدمات پرواز | مونتاژکاران سازه، سطوح پروازی، سیستم‌ها و اتصالات هواپیما | تکنسین‌های مهندسی خودرو | کارشناسان و تکنسین‌های کالیبراسیون | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصابان و تعمیرکاران سیستم‌های برقی و الکترونیکی تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | مهندسان الکترونیک، به جز رایانه | مونتاژکاران موتور و ماشین‌آلات | تکنسین‌های نور و روشنایی | مهندسان مکانیک | تکنسین‌های رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | مکانیک و تکنسین خدمات هواپیما | متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌های مهندسی خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مهندسان الکترونیک، به‌جز کامپیوتر | مونتاژکاران موتور و سایر ماشین‌آلات | تکنسین‌های نورپردازی | مهندسان مکانیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | زبان انگلیسی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی</t>
+          <t>مکانیک | تولید و فرآوری | زبان انگلیسی | مدیریت و اداره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | حساسیت به مسئله | دید نزدیک | چابکی دستی | ثبات دست و بازو | مرتب‌سازی اطلاعات | تجسم فضایی | تشخیص رنگ‌ها | استدلال قیاسی | حساسیت شنوایی | استدلال استقرایی | درک کتبی | درک شفاهی | زمان واکنش | هماهنگی اندام‌ها | دقت کنترل | سرعت ادراک | انعطاف‌پذیری در بستن الگوها | سرعت در بستن الگوها | انعطاف‌پذیری دامنه‌ای | کنترل نرخ سرعت | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | توجه شنیداری | درک عمق | بیان شفاهی</t>
+          <t>مهارت انگشتان | حساسیت به مسئله | بینایی نزدیک | مهارت دستی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | تجسم | تشخیص رنگ بصری | استدلال قیاسی | حساسیت شنوایی | استدلال استقرایی | درک کتبی | درک شفاهی | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | سرعت ادراکی | انعطاف‌پذیری بستار | سرعت بستار | انعطاف‌پذیری دامنه حرکت | کنترل نرخ | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | درک عمق | بیان شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح پروازی، سیستم‌ها و اتصالات هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران کنترلرها و شیرهای صنعتی، به جز درهای مکانیکی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصابان و تعمیرکاران سیستم‌های برقی و الکترونیکی تجهیزات حمل‌ونقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی نیروگاه‌ها، پست‌ها و رله‌ها | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و ماشین‌آلات | کارگران کمکی نصب، تعمیرات و نگهداری | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیرات و نگهداری ماشین‌آلات | نصابان و تعمیرکاران ماشین‌آلات صنعتی (میلرایت) | مکانیک‌های ماشین‌آلات سنگین متحرک، به جز موتور | مکانیک‌ها و تکنسین‌های قایق‌های موتوری | مکانیک‌های موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکاران واگن‌های قطار | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های جوشکاری، لحیم‌کاری و برزینگ</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مکانیک و تکنسین خدمات خودرو | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران کمکی نصب، نگهداری و تعمیرات | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
